--- a/method/ica_methods_codebook.xlsx
+++ b/method/ica_methods_codebook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timsc\Documents\GitHub\ica-methods-synthesis\method\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFAD2A2-441D-49C3-A13F-523DC6C326A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9B2242-4822-4D5A-9247-6D4773EF5A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
     <definedName name="language_mentioned_list">Codebook!$P$2:$P$4</definedName>
     <definedName name="length_correlation_noted_list">Codebook!$AZ$2:$AZ$4</definedName>
     <definedName name="matrix_list">Codebook!$B$2:$B$3</definedName>
-    <definedName name="matrix_source_list">Codebook!$BE$2:$BE$3</definedName>
+    <definedName name="matrix_source_list">Codebook!$BK$2:$BK$3</definedName>
     <definedName name="max_overlap_list">Codebook!$AX$2:$AX$3</definedName>
     <definedName name="mean_overlap_list">Codebook!$AT$2:$AT$3</definedName>
     <definedName name="min_overlap_list">Codebook!$AV$2:$AV$3</definedName>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="188">
   <si>
     <t>study_id</t>
   </si>
@@ -733,6 +733,74 @@
   </si>
   <si>
     <t>If the paper reports a correlation between the length of scale and the mean overlap, note the correlation.</t>
+  </si>
+  <si>
+    <t>heterogeneity_emphasized</t>
+  </si>
+  <si>
+    <t>overlap_reported</t>
+  </si>
+  <si>
+    <t>noninterchangeability_emphasized</t>
+  </si>
+  <si>
+    <t>recommend_careful_measure_selection</t>
+  </si>
+  <si>
+    <t>recommend_measure_development</t>
+  </si>
+  <si>
+    <t>ica_methods_problems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coder whether the paper explicitly emphasizes heterogeneity within their set of instruments. 
+TRUE: heterogeneity is mentioned
+FALSE: heterogeneity is not mentioned
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code the wording that is used to describe the total overlap findings, do not code if they only report overlap values
+very_weak_overlap
+weak_overlap
+moderate_overlap
+strong_overlap
+not_specified
+</t>
+  </si>
+  <si>
+    <t>Code whether the paper explicitly emphasizes that scales should not automatically be assumed to be interchangeable
+TRUE: noninterchangeability is explicitly mentioned
+FALSE: noninterchangeability is not explicitly mentioned</t>
+  </si>
+  <si>
+    <t>very_weak_overlap</t>
+  </si>
+  <si>
+    <t>weak_overlap</t>
+  </si>
+  <si>
+    <t>moderate_overlap</t>
+  </si>
+  <si>
+    <t>strong_overlap</t>
+  </si>
+  <si>
+    <t>not_specified</t>
+  </si>
+  <si>
+    <t>Code whether the paper emphasizes that measurement selection should be done carefully and selectively. 
+TRUE: careful measurement selection emphasized
+FALSE: careful measurement selection not emphasized</t>
+  </si>
+  <si>
+    <t>Code whether the paper calls for new measurements to be developed (potentially on the basis of their findings)
+TRUE: calls for development of new measurements
+FALSE: no calls for measurement development</t>
+  </si>
+  <si>
+    <t>Code whether the paper reflects on problems encountered at any stages of the analysis process (e.g. Problematic subjectivity, no clear guidelines, no clear overlap thresholds)
+TRUE: the paper reflects on problems encountered during the analysis 
+FALSE: no reflections on encountered problems</t>
   </si>
 </sst>
 </file>
@@ -777,7 +845,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -785,11 +853,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -797,6 +880,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1099,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BF19"/>
+  <dimension ref="A1:BL19"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55" customWidth="1"/>
@@ -1122,10 +1208,10 @@
     <col min="48" max="48" width="44.109375" customWidth="1"/>
     <col min="49" max="49" width="55" customWidth="1"/>
     <col min="50" max="50" width="44.109375" customWidth="1"/>
-    <col min="51" max="58" width="55" customWidth="1"/>
+    <col min="51" max="64" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1292,16 +1378,34 @@
         <v>52</v>
       </c>
       <c r="BD1" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="BE1" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BF1" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="BG1" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="BH1" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI1" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="BJ1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BK1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BL1" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:64" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>56</v>
       </c>
@@ -1438,11 +1542,29 @@
         <v>164</v>
       </c>
       <c r="BB2" s="1"/>
-      <c r="BE2" s="1" t="s">
+      <c r="BD2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>180</v>
+      </c>
+      <c r="BF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BK2" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:64" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>62</v>
       </c>
@@ -1579,11 +1701,29 @@
         <v>165</v>
       </c>
       <c r="BB3" s="1"/>
-      <c r="BE3" s="1" t="s">
+      <c r="BD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>181</v>
+      </c>
+      <c r="BF3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK3" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:64" x14ac:dyDescent="0.3">
       <c r="D4" s="1" t="s">
         <v>65</v>
       </c>
@@ -1669,8 +1809,11 @@
         <v>166</v>
       </c>
       <c r="BB4" s="1"/>
+      <c r="BE4" t="s">
+        <v>182</v>
+      </c>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:64" x14ac:dyDescent="0.3">
       <c r="D5" s="1" t="s">
         <v>144</v>
       </c>
@@ -1710,8 +1853,11 @@
       <c r="BA5" t="s">
         <v>167</v>
       </c>
+      <c r="BE5" t="s">
+        <v>183</v>
+      </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:64" x14ac:dyDescent="0.3">
       <c r="E6" s="1" t="s">
         <v>149</v>
       </c>
@@ -1736,8 +1882,11 @@
       <c r="BA6" t="s">
         <v>168</v>
       </c>
+      <c r="BE6" t="s">
+        <v>184</v>
+      </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:64" x14ac:dyDescent="0.3">
       <c r="E7" s="1" t="s">
         <v>150</v>
       </c>
@@ -1760,7 +1909,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:64" x14ac:dyDescent="0.3">
       <c r="AG8" s="1" t="s">
         <v>82</v>
       </c>
@@ -1768,7 +1917,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:64" x14ac:dyDescent="0.3">
       <c r="AG9" s="1" t="s">
         <v>83</v>
       </c>
@@ -1776,7 +1925,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:64" x14ac:dyDescent="0.3">
       <c r="AG10" s="1" t="s">
         <v>74</v>
       </c>
@@ -1784,7 +1933,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:64" x14ac:dyDescent="0.3">
       <c r="AG11" s="1" t="s">
         <v>71</v>
       </c>
@@ -1792,12 +1941,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:64" x14ac:dyDescent="0.3">
       <c r="AN12" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:58" ht="249.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:64" ht="249.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>116</v>
       </c>
@@ -1964,12 +2113,30 @@
         <v>142</v>
       </c>
       <c r="BD19" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BE19" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="BF19" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BG19" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="BH19" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="BI19" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="BJ19" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="BE19" s="3" t="s">
+      <c r="BK19" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="BF19" s="3" t="s">
+      <c r="BL19" s="3" t="s">
         <v>115</v>
       </c>
     </row>
